--- a/datosSesionesCorValues.xlsx
+++ b/datosSesionesCorValues.xlsx
@@ -533,13 +533,13 @@
         <v>0.3368882066868844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3011787587750571</v>
+        <v>0.2990529959830471</v>
       </c>
       <c r="E2" t="n">
         <v>0.2680494948348038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04243888011701599</v>
+        <v>0.3820685251888868</v>
       </c>
       <c r="G2" t="n">
         <v>0.5373128103644307</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3221770773329175</v>
+        <v>0.3231049517500959</v>
       </c>
       <c r="E3" t="n">
         <v>0.2988455388202318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1277558247137819</v>
+        <v>0.3178816350259958</v>
       </c>
       <c r="G3" t="n">
         <v>0.3840973124458718</v>
@@ -649,58 +649,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3011787587750571</v>
+        <v>0.2990529959830471</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3221770773329175</v>
+        <v>0.3231049517500959</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04502538826683948</v>
+        <v>0.04750950692625497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.163904927228775</v>
+        <v>0.7396341248896212</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6077516597880899</v>
+        <v>0.6048855911045362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5536449982487526</v>
+        <v>0.5501949156267432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6006202307209231</v>
+        <v>0.600876518824929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7025984433833732</v>
+        <v>0.6972226689346478</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6420656873828281</v>
+        <v>0.6358872819628794</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4545954456868076</v>
+        <v>0.4575301164380393</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4693815136925135</v>
+        <v>0.4688143309895726</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3938880452415908</v>
+        <v>0.3935983406282119</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4966422905447867</v>
+        <v>0.4956120040074984</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8524964670330129</v>
+        <v>0.8486944776153948</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7544328156167346</v>
+        <v>0.7524768646737829</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2604885957358143</v>
+        <v>0.2636864256628855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3100498513852949</v>
+        <v>0.3134340201079437</v>
       </c>
     </row>
     <row r="5">
@@ -716,13 +716,13 @@
         <v>0.2988455388202318</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04502538826683948</v>
+        <v>0.04750950692625497</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.127966239189512</v>
+        <v>0.08831921626791378</v>
       </c>
       <c r="G5" t="n">
         <v>0.5263601129904729</v>
@@ -771,58 +771,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04243888011701599</v>
+        <v>0.3820685251888868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1277558247137819</v>
+        <v>0.3178816350259958</v>
       </c>
       <c r="D6" t="n">
-        <v>0.163904927228775</v>
+        <v>0.7396341248896212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.127966239189512</v>
+        <v>0.08831921626791378</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08184205906335784</v>
+        <v>0.6403316203781002</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04487227587758377</v>
+        <v>0.5890395839493437</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1901374239850721</v>
+        <v>0.611782303132094</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.01278146112298162</v>
+        <v>0.6773735336157087</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05044452014480567</v>
+        <v>0.6410581682492856</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1881234755920037</v>
+        <v>0.3265911279524137</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1489386845249592</v>
+        <v>0.5447459766844475</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1338198261117954</v>
+        <v>0.4608831044754919</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1371819885387126</v>
+        <v>0.5677185632114139</v>
       </c>
       <c r="P6" t="n">
-        <v>0.07549889218967339</v>
+        <v>0.7916777152582183</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1360946856039542</v>
+        <v>0.7344654915818482</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2486576557940962</v>
+        <v>0.3716552256050685</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2555532367274533</v>
+        <v>0.3883175855391278</v>
       </c>
     </row>
     <row r="7">
@@ -838,13 +838,13 @@
         <v>0.3840973124458718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6077516597880899</v>
+        <v>0.6048855911045362</v>
       </c>
       <c r="E7" t="n">
         <v>0.5263601129904729</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08184205906335784</v>
+        <v>0.6403316203781002</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.3919508473014646</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5536449982487526</v>
+        <v>0.5501949156267432</v>
       </c>
       <c r="E8" t="n">
         <v>0.5563234843034293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04487227587758377</v>
+        <v>0.5890395839493437</v>
       </c>
       <c r="G8" t="n">
         <v>0.982363218945558</v>
@@ -960,13 +960,13 @@
         <v>0.2248222116317658</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6006202307209231</v>
+        <v>0.600876518824929</v>
       </c>
       <c r="E9" t="n">
         <v>0.2374195546817355</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1901374239850721</v>
+        <v>0.611782303132094</v>
       </c>
       <c r="G9" t="n">
         <v>0.7254993268881513</v>
@@ -1021,13 +1021,13 @@
         <v>0.3868028892064488</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7025984433833732</v>
+        <v>0.6972226689346478</v>
       </c>
       <c r="E10" t="n">
         <v>0.4408659417857475</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.01278146112298162</v>
+        <v>0.6773735336157087</v>
       </c>
       <c r="G10" t="n">
         <v>0.9277387325162607</v>
@@ -1082,13 +1082,13 @@
         <v>0.3841587953502379</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6420656873828281</v>
+        <v>0.6358872819628794</v>
       </c>
       <c r="E11" t="n">
         <v>0.4334049733609505</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.05044452014480567</v>
+        <v>0.6410581682492856</v>
       </c>
       <c r="G11" t="n">
         <v>0.921011734513043</v>
@@ -1143,13 +1143,13 @@
         <v>0.09482795892005802</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4545954456868076</v>
+        <v>0.4575301164380393</v>
       </c>
       <c r="E12" t="n">
         <v>0.1306136158342957</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1881234755920037</v>
+        <v>0.3265911279524137</v>
       </c>
       <c r="G12" t="n">
         <v>0.2293944249264855</v>
@@ -1204,13 +1204,13 @@
         <v>0.3423381319913773</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4693815136925135</v>
+        <v>0.4688143309895726</v>
       </c>
       <c r="E13" t="n">
         <v>0.5403404875754924</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1489386845249592</v>
+        <v>0.5447459766844475</v>
       </c>
       <c r="G13" t="n">
         <v>0.9545860290038037</v>
@@ -1265,13 +1265,13 @@
         <v>0.3488371319439474</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3938880452415908</v>
+        <v>0.3935983406282119</v>
       </c>
       <c r="E14" t="n">
         <v>0.6063465746472997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1338198261117954</v>
+        <v>0.4608831044754919</v>
       </c>
       <c r="G14" t="n">
         <v>0.9158876346809195</v>
@@ -1326,13 +1326,13 @@
         <v>0.2200466606680969</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4966422905447867</v>
+        <v>0.4956120040074984</v>
       </c>
       <c r="E15" t="n">
         <v>0.2185650221690343</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1371819885387126</v>
+        <v>0.5677185632114139</v>
       </c>
       <c r="G15" t="n">
         <v>0.7448138833605551</v>
@@ -1387,13 +1387,13 @@
         <v>0.4107345749410297</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8524964670330129</v>
+        <v>0.8486944776153948</v>
       </c>
       <c r="E16" t="n">
         <v>0.3216170974200823</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07549889218967339</v>
+        <v>0.7916777152582183</v>
       </c>
       <c r="G16" t="n">
         <v>0.8277727625893223</v>
@@ -1448,13 +1448,13 @@
         <v>0.3798510760743963</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7544328156167346</v>
+        <v>0.7524768646737829</v>
       </c>
       <c r="E17" t="n">
         <v>0.381094977020497</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1360946856039542</v>
+        <v>0.7344654915818482</v>
       </c>
       <c r="G17" t="n">
         <v>0.8459764839465486</v>
@@ -1509,13 +1509,13 @@
         <v>0.2419176145091841</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2604885957358143</v>
+        <v>0.2636864256628855</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2219062374208031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2486576557940962</v>
+        <v>0.3716552256050685</v>
       </c>
       <c r="G18" t="n">
         <v>-0.06050381548290676</v>
@@ -1570,13 +1570,13 @@
         <v>0.2581269601251902</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3100498513852949</v>
+        <v>0.3134340201079437</v>
       </c>
       <c r="E19" t="n">
         <v>-0.138831227916319</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2555532367274533</v>
+        <v>0.3883175855391278</v>
       </c>
       <c r="G19" t="n">
         <v>-0.01183789197245073</v>
